--- a/GrupoChasis/Materiales a Inventario_2026.xlsx
+++ b/GrupoChasis/Materiales a Inventario_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioviedo-my.sharepoint.com/personal/uo288008_uniovi_es/Documents/MASTER/Segundo/Proyecto 2-Desarrollo Sistema Mecatrónico Industrial/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irene. C. T\Desktop\G1_Project_Rover2026\GrupoChasis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="886" documentId="13_ncr:1_{4D764426-EBA0-4279-9854-F6858A2D3AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CA29FE6-5615-45F1-B364-EB247DB9182E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DB4031-22C8-4C25-AF73-A71607A5CEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -997,7 +997,7 @@
     <dxf>
       <border outline="0">
         <top style="medium">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
       </border>
     </dxf>
@@ -1069,7 +1069,7 @@
     <dxf>
       <border outline="0">
         <top style="medium">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
@@ -1174,7 +1174,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8CB0E0DB-3A17-4D9B-930B-4B8A23D8A8C1}" name="Tabla1" displayName="Tabla1" ref="B4:L68" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8CB0E0DB-3A17-4D9B-930B-4B8A23D8A8C1}" name="Tabla1" displayName="Tabla1" ref="B4:L68" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="B4:L68" xr:uid="{8CB0E0DB-3A17-4D9B-930B-4B8A23D8A8C1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K65">
     <sortCondition ref="B5:B65"/>
@@ -1183,22 +1183,22 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{A4850259-7CEE-4B17-9046-211427BECAD3}" name="Familia"/>
     <tableColumn id="2" xr3:uid="{C7CCB13A-E5FE-418D-BF9D-A5A84B59E308}" name="Componente"/>
-    <tableColumn id="3" xr3:uid="{594EE141-5B6C-4A6F-8A70-0FD6EA739ED2}" name="Proveedor" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{3688498B-D58D-435A-9E60-BC845888329B}" name="Ref. Proveedor" dataDxfId="19" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="5" xr3:uid="{283B1C87-797B-4469-B2F2-DEEDBF7D94CA}" name="Fabricante" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{3D9D107D-96F8-44BA-B969-9C373122095A}" name="Ref. Fabricante" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{288DA235-56B0-435D-8745-7DE7E171AB9A}" name="Ctd" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{885D9E79-A106-4F9E-AFFB-F34FFD3F6205}" name="Unidad" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{A035024D-DB3B-42A4-955E-4AC6B98A4651}" name="Ubicación" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{0158F271-1106-4513-8A94-1C8372065E06}" name="Comprada" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{9037693D-CC1A-44C3-BC35-30D95E2BE13C}" name="Columna1" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{594EE141-5B6C-4A6F-8A70-0FD6EA739ED2}" name="Proveedor" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{3688498B-D58D-435A-9E60-BC845888329B}" name="Ref. Proveedor" dataDxfId="7" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="5" xr3:uid="{283B1C87-797B-4469-B2F2-DEEDBF7D94CA}" name="Fabricante" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{3D9D107D-96F8-44BA-B969-9C373122095A}" name="Ref. Fabricante" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{288DA235-56B0-435D-8745-7DE7E171AB9A}" name="Ctd" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{885D9E79-A106-4F9E-AFFB-F34FFD3F6205}" name="Unidad" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{A035024D-DB3B-42A4-955E-4AC6B98A4651}" name="Ubicación" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{0158F271-1106-4513-8A94-1C8372065E06}" name="Comprada" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{9037693D-CC1A-44C3-BC35-30D95E2BE13C}" name="Columna1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{55D581FE-F9E4-415B-A2FC-7A11F89B18D8}" name="Tabla13" displayName="Tabla13" ref="B4:L68" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{55D581FE-F9E4-415B-A2FC-7A11F89B18D8}" name="Tabla13" displayName="Tabla13" ref="B4:L68" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
   <autoFilter ref="B4:L68" xr:uid="{8CB0E0DB-3A17-4D9B-930B-4B8A23D8A8C1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K65">
     <sortCondition ref="B5:B65"/>
@@ -1207,15 +1207,15 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{8BA3F889-6763-4F05-A91E-F9DA82C6EFB5}" name="Familia"/>
     <tableColumn id="2" xr3:uid="{CFAA7382-63DA-4587-8729-381743D29A5F}" name="Componente"/>
-    <tableColumn id="3" xr3:uid="{CC64FDC8-7FC1-49AF-8C62-A97318BC3841}" name="Proveedor" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{BC2C2C06-4275-40A9-9EA3-A865743779AB}" name="Ref. Proveedor" dataDxfId="7" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="5" xr3:uid="{619AAB46-10A9-471E-81B6-0B8789BFE1C2}" name="Fabricante" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{0A95565F-990E-4592-9214-CAC7E4E1418F}" name="Ref. Fabricante" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{8B5B77D4-949A-419A-ABB1-FA7FCDFD4B24}" name="Ctd" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{C0FF2592-0E43-44CA-8040-7C54EE299A8A}" name="Unidad" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{226F158D-BCCC-4A98-B61A-710071E95680}" name="Ubicación" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{47DDF2BC-09B1-46AB-BFAA-7925526A7201}" name="Comprada" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{ADF04AA5-4F5D-4013-A9E2-1D02D58C6359}" name="Columna1" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{CC64FDC8-7FC1-49AF-8C62-A97318BC3841}" name="Proveedor" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{BC2C2C06-4275-40A9-9EA3-A865743779AB}" name="Ref. Proveedor" dataDxfId="19" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="5" xr3:uid="{619AAB46-10A9-471E-81B6-0B8789BFE1C2}" name="Fabricante" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{0A95565F-990E-4592-9214-CAC7E4E1418F}" name="Ref. Fabricante" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{8B5B77D4-949A-419A-ABB1-FA7FCDFD4B24}" name="Ctd" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{C0FF2592-0E43-44CA-8040-7C54EE299A8A}" name="Unidad" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{226F158D-BCCC-4A98-B61A-710071E95680}" name="Ubicación" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{47DDF2BC-09B1-46AB-BFAA-7925526A7201}" name="Comprada" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{ADF04AA5-4F5D-4013-A9E2-1D02D58C6359}" name="Columna1" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5025,38 +5025,38 @@
       </c>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B50" t="s">
+    <row r="50" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H50" s="23">
         <v>18</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K50" s="4">
-        <v>2024</v>
-      </c>
-      <c r="L50" s="1"/>
+      <c r="I50" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J50" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="K50" s="23">
+        <v>2024</v>
+      </c>
+      <c r="L50" s="23"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
@@ -5647,12 +5647,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="75e5e99f-056a-4a24-8bc1-9a92463d9cd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b7ea243d-c580-49a0-ab1d-05d2dfc7a441" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5863,20 +5865,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="75e5e99f-056a-4a24-8bc1-9a92463d9cd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b7ea243d-c580-49a0-ab1d-05d2dfc7a441" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC1831E1-7EC3-4358-A817-5BC3B204D32E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DF4CB2-747F-4C41-9B27-52D0BB07E1E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="75e5e99f-056a-4a24-8bc1-9a92463d9cd4"/>
+    <ds:schemaRef ds:uri="b7ea243d-c580-49a0-ab1d-05d2dfc7a441"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5901,12 +5904,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DF4CB2-747F-4C41-9B27-52D0BB07E1E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC1831E1-7EC3-4358-A817-5BC3B204D32E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="75e5e99f-056a-4a24-8bc1-9a92463d9cd4"/>
-    <ds:schemaRef ds:uri="b7ea243d-c580-49a0-ab1d-05d2dfc7a441"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GrupoChasis/Materiales a Inventario_2026.xlsx
+++ b/GrupoChasis/Materiales a Inventario_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irene. C. T\Desktop\G1_Project_Rover2026\GrupoChasis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DB4031-22C8-4C25-AF73-A71607A5CEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEAB93C-A586-4456-A821-AC2F7C6270FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5025,71 +5025,71 @@
       </c>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="22" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" t="s">
         <v>74</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E50" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="23" t="s">
+      <c r="F50" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G50" s="23" t="s">
+      <c r="G50" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H50" s="23">
+      <c r="H50" s="4">
         <v>18</v>
       </c>
-      <c r="I50" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="J50" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="K50" s="23">
-        <v>2024</v>
-      </c>
-      <c r="L50" s="23"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B51" t="s">
+      <c r="I50" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K50" s="4">
+        <v>2024</v>
+      </c>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="23">
         <v>8</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K51" s="15">
+      <c r="I51" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="K51" s="23">
         <v>2025</v>
       </c>
-      <c r="L51" s="1"/>
+      <c r="L51" s="23"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B52" t="s">

--- a/GrupoChasis/Materiales a Inventario_2026.xlsx
+++ b/GrupoChasis/Materiales a Inventario_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irene. C. T\Desktop\G1_Project_Rover2026\GrupoChasis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEAB93C-A586-4456-A821-AC2F7C6270FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C57754-31DD-4509-B5A9-AF4A86517E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5647,14 +5647,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="75e5e99f-056a-4a24-8bc1-9a92463d9cd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b7ea243d-c580-49a0-ab1d-05d2dfc7a441" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5865,21 +5863,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="75e5e99f-056a-4a24-8bc1-9a92463d9cd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b7ea243d-c580-49a0-ab1d-05d2dfc7a441" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DF4CB2-747F-4C41-9B27-52D0BB07E1E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC1831E1-7EC3-4358-A817-5BC3B204D32E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="75e5e99f-056a-4a24-8bc1-9a92463d9cd4"/>
-    <ds:schemaRef ds:uri="b7ea243d-c580-49a0-ab1d-05d2dfc7a441"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5904,9 +5901,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC1831E1-7EC3-4358-A817-5BC3B204D32E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DF4CB2-747F-4C41-9B27-52D0BB07E1E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="75e5e99f-056a-4a24-8bc1-9a92463d9cd4"/>
+    <ds:schemaRef ds:uri="b7ea243d-c580-49a0-ab1d-05d2dfc7a441"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
